--- a/results/Int All Data -1.0/Rando_1_permute.xlsx
+++ b/results/Int All Data -1.0/Rando_1_permute.xlsx
@@ -440,127 +440,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8141291983814832</v>
+        <v>0.8097224187204664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8144681814323307</v>
+        <v>0.812434283127246</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8042124821972592</v>
+        <v>0.8123735415900324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7982577365288663</v>
+        <v>0.8123128000528188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7993707025834017</v>
+        <v>0.8112958509002763</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.799588202559822</v>
+        <v>0.8084683512068136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7993354272186224</v>
+        <v>0.8101025249238373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7993354272186224</v>
+        <v>0.8107197494883185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7989964441677748</v>
+        <v>0.8147268045612744</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7970585627646831</v>
+        <v>0.7982479273365213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.803812757609198</v>
+        <v>0.7950050460749083</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8078805542193674</v>
+        <v>0.7950050460749083</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8061856389651303</v>
+        <v>0.7953440291257557</v>
       </c>
     </row>
     <row r="15">
@@ -570,1417 +570,1417 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8026135838450148</v>
+        <v>0.7925714231817624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8026135838450148</v>
+        <v>0.7935629061618705</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8013536685436179</v>
+        <v>0.7944583722399856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8013536685436179</v>
+        <v>0.7951363383416805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7974426303726549</v>
+        <v>0.791346783245145</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7970330965922489</v>
+        <v>0.7917210416607716</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7977110626939438</v>
+        <v>0.7916406817388679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7977110626939438</v>
+        <v>0.7916406817388679</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7943212321854691</v>
+        <v>0.7935432877771804</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7937294737934222</v>
+        <v>0.7931435631891193</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7937294737934222</v>
+        <v>0.7836207238052121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8041419314677004</v>
+        <v>0.7854469313262217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8088876941795649</v>
+        <v>0.7854469313262217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8085487111287173</v>
+        <v>0.785386189789008</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8069145374116937</v>
+        <v>0.7850472067381606</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8072182450977619</v>
+        <v>0.7867421219923979</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8054018467690973</v>
+        <v>0.7961376305141337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8062169529253087</v>
+        <v>0.7916348339511239</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8102494741706988</v>
+        <v>0.796754855078615</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8154557030078379</v>
+        <v>0.7987887533836998</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8149952368825633</v>
+        <v>0.8001799609518689</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8200799826452752</v>
+        <v>0.7969625458626901</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8182635843166106</v>
+        <v>0.7975543042547372</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8227507238995313</v>
+        <v>0.7947816983107439</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8281842619054356</v>
+        <v>0.8044299821736793</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8177208718862888</v>
+        <v>0.8047689652245267</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8089778632938136</v>
+        <v>0.8093579694971846</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8094990709563019</v>
+        <v>0.8103749186497269</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8105062109164992</v>
+        <v>0.8113918678022694</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8127928845627835</v>
+        <v>0.8113918678022694</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8138960414249738</v>
+        <v>0.8017083085745546</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8075161049960857</v>
+        <v>0.8026645161898833</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8081940710977806</v>
+        <v>0.8029427577035171</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8230838591626345</v>
+        <v>0.7951461475340256</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.819016062552465</v>
+        <v>0.7885075879761938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.819016062552465</v>
+        <v>0.7877081388000717</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8067145807985059</v>
+        <v>0.7887858294898278</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.811511275855239</v>
+        <v>0.7886643464154004</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8000073568942587</v>
+        <v>0.7986770795016176</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7986514246908689</v>
+        <v>0.8034835837506956</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8041809795987662</v>
+        <v>0.8039793252407497</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8034422719598577</v>
+        <v>0.8009284777831225</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7992628014676061</v>
+        <v>0.7909764862341191</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7907078652745159</v>
+        <v>0.7985555964271903</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7801680767380663</v>
+        <v>0.7949482659422955</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7772994538920801</v>
+        <v>0.7925753845863633</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7751695386850024</v>
+        <v>0.7754440074323496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7789787121662282</v>
+        <v>0.7754440074323496</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7789787121662282</v>
+        <v>0.7754440074323496</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8170310215707912</v>
+        <v>0.7704552785716308</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8094479499731191</v>
+        <v>0.7544015921073729</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8093872084359055</v>
+        <v>0.7430936683549796</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8097261914867528</v>
+        <v>0.7367999396357394</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8129788819407109</v>
+        <v>0.7355654905067768</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8093872084359055</v>
+        <v>0.7355654905067768</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8046669118964753</v>
+        <v>0.7355654905067768</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8135921451005914</v>
+        <v>0.7410499608575498</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.811097780670232</v>
+        <v>0.746073965083048</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8129494543636758</v>
+        <v>0.7474200880940929</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8217552795148222</v>
+        <v>0.7484723126114146</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8214966563858785</v>
+        <v>0.749201211057978</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8172309781839789</v>
+        <v>0.7476885204153816</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8182577365288664</v>
+        <v>0.7433424822915782</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8344387538552955</v>
+        <v>0.7463737113645152</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8111509766748723</v>
+        <v>0.7414104486762306</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8054588155400244</v>
+        <v>0.7448864868943531</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7839382020882262</v>
+        <v>0.7438695377418107</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7850922912952849</v>
+        <v>0.7438695377418107</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.785977948181055</v>
+        <v>0.7438695377418107</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7782068041839978</v>
+        <v>0.7414359148486649</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7724244739349009</v>
+        <v>0.7423921224639937</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7704062326099054</v>
+        <v>0.7425077577506767</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7327791139658376</v>
+        <v>0.739882101053545</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.712208860341624</v>
+        <v>0.7282821651905719</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7083585637078748</v>
+        <v>0.6732082661309339</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6677413391433934</v>
+        <v>0.6713311262650556</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6680195806570273</v>
+        <v>0.6837167407072051</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6862697716533205</v>
+        <v>0.6685585203210624</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6862697716533205</v>
+        <v>0.6626233930373598</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6840889241013742</v>
+        <v>0.6464071003461513</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6960297293983381</v>
+        <v>0.6481980325023815</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6850862548692265</v>
+        <v>0.6469028418362053</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6369955575676975</v>
+        <v>0.6655586052083039</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6403853880761722</v>
+        <v>0.6658368467219377</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6403853880761722</v>
+        <v>0.6428154268413457</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.603103100270696</v>
+        <v>0.6413987531007423</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6141582486818897</v>
+        <v>0.6113488582666026</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6369329296473407</v>
+        <v>0.608464578440527</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6488875055412504</v>
+        <v>0.5270128179734586</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6491050055176707</v>
+        <v>0.5263348518717637</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6491050055176707</v>
+        <v>0.5253179027192213</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6603169123680711</v>
+        <v>0.5280552332984353</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.674803014440263</v>
+        <v>0.5285509747884893</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6277449232713657</v>
+        <v>0.5248829027663808</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6318911934202955</v>
+        <v>0.5282629240825104</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6143346255057864</v>
+        <v>0.5274634749063882</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6145521254822066</v>
+        <v>0.5274634749063882</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6114914688322345</v>
+        <v>0.5301145977759543</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6009399847202965</v>
+        <v>0.5297756147251068</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5791077407732285</v>
+        <v>0.5290976486234119</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5714071475057299</v>
+        <v>0.5290976486234119</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5714071475057299</v>
+        <v>0.5290976486234119</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5215000518755364</v>
+        <v>0.5250905935504561</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5039453703441706</v>
+        <v>0.5269168010714657</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5034849042188959</v>
+        <v>0.5272557841223131</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5230068947303887</v>
+        <v>0.522145572187167</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5061262178961169</v>
+        <v>0.5186851909491337</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4615687162219518</v>
+        <v>0.5191711232468427</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4894498363562623</v>
+        <v>0.5219084538260567</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5353421427426125</v>
+        <v>0.5248025428444771</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.531654452335814</v>
+        <v>0.523613178272639</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5334101091272648</v>
+        <v>0.523613178272639</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5375993888118616</v>
+        <v>0.543907076766362</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5301808098242834</v>
+        <v>0.5501655301208228</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5312585005140394</v>
+        <v>0.5492093225054941</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5345973986776454</v>
+        <v>0.5424649368533243</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5210326061326316</v>
+        <v>0.5424649368533243</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5221004876300426</v>
+        <v>0.5424649368533243</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5223787291436763</v>
+        <v>0.5534750007073936</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5220397460928289</v>
+        <v>0.5330086867943747</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5124972883242315</v>
+        <v>0.5330086867943747</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5115410807089028</v>
+        <v>0.5251513350876696</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5138786867000557</v>
+        <v>0.5221612291672562</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5188223310036502</v>
+        <v>0.519702140101676</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5190398309800703</v>
+        <v>0.5207798307914321</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5162770342284221</v>
+        <v>0.5224747460456693</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5209973307678523</v>
+        <v>0.5095679239410317</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5213363138186997</v>
+        <v>0.5092896824273978</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5296188562859002</v>
+        <v>0.506360318044198</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.519798157003669</v>
+        <v>0.5050749365703668</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5132105297907058</v>
+        <v>0.5087077332276959</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5137728606057176</v>
+        <v>0.5061879026249022</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5208660385010799</v>
+        <v>0.5189732416551126</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5216047461399885</v>
+        <v>0.5131752544259265</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.529107457815757</v>
+        <v>0.5117938560501023</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5263250426794186</v>
+        <v>0.5111158899484074</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5214323307206927</v>
+        <v>0.5111158899484074</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5089605085688954</v>
+        <v>0.5093602331569566</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5024845552380144</v>
+        <v>0.5091074578157569</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5022063137243805</v>
+        <v>0.4994689831451666</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5012755722814861</v>
+        <v>0.499408241607953</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4975467587221641</v>
+        <v>0.4998687077332277</v>
       </c>
     </row>
   </sheetData>
